--- a/data/trans_orig/P16A_2_R3-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A_2_R3-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72442</t>
+          <t>72832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111527</t>
+          <t>110461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112647</t>
+          <t>113308</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141372</t>
+          <t>141176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>192158</t>
+          <t>195929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>240977</t>
+          <t>241844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199916</t>
+          <t>200982</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239001</t>
+          <t>238611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148263</t>
+          <t>148459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176988</t>
+          <t>176327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>360100</t>
+          <t>359233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>408919</t>
+          <t>405148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,4%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94353</t>
+          <t>95867</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>136832</t>
+          <t>138103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187304</t>
+          <t>188674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>227199</t>
+          <t>224786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>292750</t>
+          <t>291561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>357708</t>
+          <t>352569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>381558</t>
+          <t>380287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>424037</t>
+          <t>422523</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>287770</t>
+          <t>290183</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327665</t>
+          <t>326295</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>675651</t>
+          <t>680790</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>740609</t>
+          <t>741798</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75362</t>
+          <t>73798</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105498</t>
+          <t>107228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130163</t>
+          <t>130058</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161585</t>
+          <t>161027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>214463</t>
+          <t>212503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256989</t>
+          <t>258263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210552</t>
+          <t>208822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>240688</t>
+          <t>242252</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187543</t>
+          <t>188101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218965</t>
+          <t>219070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>408189</t>
+          <t>406915</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>450715</t>
+          <t>452675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76340</t>
+          <t>77197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116789</t>
+          <t>117054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97614</t>
+          <t>95377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>209430</t>
+          <t>208940</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192996</t>
+          <t>186450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>303331</t>
+          <t>302107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195768</t>
+          <t>195503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>236217</t>
+          <t>235360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>266288</t>
+          <t>266778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378104</t>
+          <t>380341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>484943</t>
+          <t>486167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>595278</t>
+          <t>601824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>76,35%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32845</t>
+          <t>32297</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50783</t>
+          <t>50210</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41700</t>
+          <t>42450</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102631</t>
+          <t>103285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82349</t>
+          <t>82447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141578</t>
+          <t>142941</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127959</t>
+          <t>128532</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145897</t>
+          <t>146445</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156148</t>
+          <t>155494</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217079</t>
+          <t>216329</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>295943</t>
+          <t>294580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>355172</t>
+          <t>355074</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66300</t>
+          <t>66137</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92050</t>
+          <t>92584</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>98361</t>
+          <t>97932</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123803</t>
+          <t>123691</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>170246</t>
+          <t>170129</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>206528</t>
+          <t>207301</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177586</t>
+          <t>177052</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203336</t>
+          <t>203499</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133253</t>
+          <t>133365</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158695</t>
+          <t>159124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>320164</t>
+          <t>319391</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>356446</t>
+          <t>356563</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>141199</t>
+          <t>140484</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>194558</t>
+          <t>193664</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>334625</t>
+          <t>334375</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>640917</t>
+          <t>658549</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>485308</t>
+          <t>480464</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>966043</t>
+          <t>937810</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>63,64%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>429721</t>
+          <t>430615</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>483080</t>
+          <t>483795</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>208348</t>
+          <t>190716</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>514640</t>
+          <t>514890</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>507501</t>
+          <t>535734</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>988236</t>
+          <t>993080</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,39%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39996</t>
+          <t>44895</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133299</t>
+          <t>133373</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>198347</t>
+          <t>198708</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>241324</t>
+          <t>241061</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>197986</t>
+          <t>192780</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>374088</t>
+          <t>377735</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>795421</t>
+          <t>795347</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>888724</t>
+          <t>883825</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>476407</t>
+          <t>476670</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>519384</t>
+          <t>519023</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1272364</t>
+          <t>1268717</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1448466</t>
+          <t>1453672</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>594040</t>
+          <t>599658</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>847131</t>
+          <t>852926</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1367959</t>
+          <t>1371287</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1946538</t>
+          <t>1936484</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2059043</t>
+          <t>2068179</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2757995</t>
+          <t>2703878</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2612686</t>
+          <t>2606891</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2865777</t>
+          <t>2860159</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1765742</t>
+          <t>1775796</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2344321</t>
+          <t>2340993</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4414102</t>
+          <t>4468219</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5113054</t>
+          <t>5103918</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_2_R3-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A_2_R3-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>90052</t>
+          <t>93494</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72832</t>
+          <t>79208</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110461</t>
+          <t>112668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>127327</t>
+          <t>136010</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113308</t>
+          <t>121828</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141176</t>
+          <t>149694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>217380</t>
+          <t>229504</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>195929</t>
+          <t>206578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>241844</t>
+          <t>251518</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>221391</t>
+          <t>225351</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>200982</t>
+          <t>206177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238611</t>
+          <t>239637</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>162308</t>
+          <t>180051</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148459</t>
+          <t>166367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176327</t>
+          <t>194233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>383697</t>
+          <t>405402</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>359233</t>
+          <t>383388</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>405148</t>
+          <t>428328</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>115416</t>
+          <t>118849</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95867</t>
+          <t>99225</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138103</t>
+          <t>144034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>207405</t>
+          <t>215600</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>188674</t>
+          <t>195164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224786</t>
+          <t>235422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>322821</t>
+          <t>334449</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>291561</t>
+          <t>303055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>352569</t>
+          <t>367243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>402974</t>
+          <t>411798</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>380287</t>
+          <t>386613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422523</t>
+          <t>431422</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>307564</t>
+          <t>330894</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>290183</t>
+          <t>311072</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>326295</t>
+          <t>351330</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>710538</t>
+          <t>742692</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>680790</t>
+          <t>709898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>741798</t>
+          <t>774086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89583</t>
+          <t>91576</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73798</t>
+          <t>76950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107228</t>
+          <t>108343</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>145314</t>
+          <t>150577</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130058</t>
+          <t>136090</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161027</t>
+          <t>166926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>234897</t>
+          <t>242153</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>212503</t>
+          <t>219847</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>258263</t>
+          <t>264621</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>226467</t>
+          <t>224417</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>208822</t>
+          <t>207650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>242252</t>
+          <t>239043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>203814</t>
+          <t>205804</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>188101</t>
+          <t>189455</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>219070</t>
+          <t>220291</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>430281</t>
+          <t>430222</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>406915</t>
+          <t>407754</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>452675</t>
+          <t>452528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>109647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77197</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117054</t>
+          <t>133147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>164857</t>
+          <t>181928</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95377</t>
+          <t>163948</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208940</t>
+          <t>201812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>260005</t>
+          <t>291576</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186450</t>
+          <t>262831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302107</t>
+          <t>323780</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>217409</t>
+          <t>263498</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195503</t>
+          <t>239998</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235360</t>
+          <t>286524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>310861</t>
+          <t>240033</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>266778</t>
+          <t>220149</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>380341</t>
+          <t>258013</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>528269</t>
+          <t>503531</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>486167</t>
+          <t>471327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>601824</t>
+          <t>532276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>66,94%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>41135</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>34595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50210</t>
+          <t>53887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>80539</t>
+          <t>84030</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42450</t>
+          <t>74754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103285</t>
+          <t>94412</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>121674</t>
+          <t>127909</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82447</t>
+          <t>115021</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142941</t>
+          <t>143760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>137607</t>
+          <t>161786</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128532</t>
+          <t>151778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146445</t>
+          <t>171070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>178240</t>
+          <t>144888</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155494</t>
+          <t>134506</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216329</t>
+          <t>154164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>315847</t>
+          <t>306673</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>294580</t>
+          <t>290822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>355074</t>
+          <t>319561</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78217</t>
+          <t>76355</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66137</t>
+          <t>64009</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92584</t>
+          <t>88787</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>110374</t>
+          <t>112564</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>97932</t>
+          <t>99464</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123691</t>
+          <t>125425</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>188591</t>
+          <t>188919</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>170129</t>
+          <t>170292</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>207301</t>
+          <t>206234</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>191419</t>
+          <t>194352</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177052</t>
+          <t>181920</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203499</t>
+          <t>206698</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>146682</t>
+          <t>151186</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133365</t>
+          <t>138325</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159124</t>
+          <t>164286</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>338101</t>
+          <t>345538</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>319391</t>
+          <t>328223</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>356563</t>
+          <t>364165</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>164916</t>
+          <t>190420</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140484</t>
+          <t>165663</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>193664</t>
+          <t>220064</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>466963</t>
+          <t>311294</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>334375</t>
+          <t>284270</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>658549</t>
+          <t>334413</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>631879</t>
+          <t>501714</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>480464</t>
+          <t>468238</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>937810</t>
+          <t>539109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>459363</t>
+          <t>529267</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>430615</t>
+          <t>499623</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>483795</t>
+          <t>554024</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>382302</t>
+          <t>460763</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190716</t>
+          <t>437644</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>514890</t>
+          <t>487787</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>841665</t>
+          <t>990030</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>535734</t>
+          <t>952635</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>993080</t>
+          <t>1023506</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>68,61%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>92432</t>
+          <t>103814</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44895</t>
+          <t>87051</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133373</t>
+          <t>124989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>219175</t>
+          <t>247637</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>198708</t>
+          <t>225292</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>241061</t>
+          <t>272553</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>311607</t>
+          <t>351451</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>192780</t>
+          <t>322253</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>377735</t>
+          <t>382323</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>836288</t>
+          <t>694258</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>795347</t>
+          <t>673083</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>883825</t>
+          <t>711021</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>498556</t>
+          <t>583694</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>476670</t>
+          <t>558778</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>519023</t>
+          <t>606039</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1334845</t>
+          <t>1277952</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1268717</t>
+          <t>1247080</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1453672</t>
+          <t>1307150</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>766900</t>
+          <t>828035</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>599658</t>
+          <t>775545</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>852926</t>
+          <t>887853</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1521954</t>
+          <t>1439640</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1371287</t>
+          <t>1390477</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1936484</t>
+          <t>1492474</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2288854</t>
+          <t>2267675</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2068179</t>
+          <t>2189604</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2703878</t>
+          <t>2347341</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2692917</t>
+          <t>2704727</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2606891</t>
+          <t>2644909</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2860159</t>
+          <t>2757217</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2190326</t>
+          <t>2297314</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1775796</t>
+          <t>2244480</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2340993</t>
+          <t>2346477</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4883243</t>
+          <t>5002041</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4468219</t>
+          <t>4922375</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5103918</t>
+          <t>5080112</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
